--- a/BMC.xlsx
+++ b/BMC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\VSCodeProject\BMC\BMC-Visualizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9349FD21-4A6E-4DDE-9819-2493D72E3EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEE0E17-FDB3-409C-8925-4B9CEBDB80F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
   <si>
     <t>Block</t>
   </si>
@@ -103,12 +103,6 @@
     <t>Performance improvement through data provided by clients</t>
   </si>
   <si>
-    <t>Website</t>
-  </si>
-  <si>
-    <t>App (Android IOS)</t>
-  </si>
-  <si>
     <t>Teenagers want to look cool</t>
   </si>
   <si>
@@ -133,12 +127,6 @@
     <t>Subscription plans</t>
   </si>
   <si>
-    <t>Ads for clothes brands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Third parties Integration </t>
-  </si>
-  <si>
     <t>how user data is legally collected or protected</t>
   </si>
   <si>
@@ -166,19 +154,76 @@
     <t>Fashion brands</t>
   </si>
   <si>
-    <t>Integration in shopping platforms</t>
-  </si>
-  <si>
     <t>Online shopping platform</t>
   </si>
   <si>
-    <t>Community build</t>
-  </si>
-  <si>
-    <t>Clothes coupon</t>
-  </si>
-  <si>
     <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Inventory check of online store or nearest local store</t>
+  </si>
+  <si>
+    <t>Seamless integration with shopping platforms</t>
+  </si>
+  <si>
+    <t>Plan complete looks for work, parties, travel, or daily wear with ease</t>
+  </si>
+  <si>
+    <t>Mobile-first chatbot interface for real-time, on-the-go fashion guidance</t>
+  </si>
+  <si>
+    <t>Self-service</t>
+  </si>
+  <si>
+    <t>Automated-service</t>
+  </si>
+  <si>
+    <t>Personalized onboarding &amp; integration with fashion brands</t>
+  </si>
+  <si>
+    <t>Mobile app / Website chatbot</t>
+  </si>
+  <si>
+    <t>Social media platforms (Instagram, TikTok, Pinterest)</t>
+  </si>
+  <si>
+    <t>Online communities &amp; forums (Reddit, Facebook Groups)</t>
+  </si>
+  <si>
+    <t>Influencer marketing &amp; fashion bloggers</t>
+  </si>
+  <si>
+    <t>Direct sales outreach (email, LinkedIn)</t>
+  </si>
+  <si>
+    <t>Fashion trade shows &amp; tech expos</t>
+  </si>
+  <si>
+    <t>Strategic partnerships with fashion platforms</t>
+  </si>
+  <si>
+    <t>Targeted digital ads (LinkedIn, industry blogs)</t>
+  </si>
+  <si>
+    <t>B2B SaaS marketplaces (e.g., Shopify App Store, HubSpot integrations)</t>
+  </si>
+  <si>
+    <t>Monthly/Annual subscriptions</t>
+  </si>
+  <si>
+    <t>In-app purchases</t>
+  </si>
+  <si>
+    <t>Ad placements</t>
+  </si>
+  <si>
+    <t>SaaS subscription fees</t>
+  </si>
+  <si>
+    <t>White-label licensing to embed chatbot tech into brand websites/apps</t>
+  </si>
+  <si>
+    <t>Revenue sharing or commission from increased sales driven by the chatbot</t>
   </si>
 </sst>
 </file>
@@ -261,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -273,6 +318,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,14 +626,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.453125" customWidth="1"/>
-    <col min="2" max="2" width="74.1796875" customWidth="1"/>
+    <col min="1" max="1" width="32.44140625" customWidth="1"/>
+    <col min="2" max="2" width="74.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,62 +644,62 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -662,411 +710,543 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
       <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
         <v>26</v>
       </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>7</v>
       </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>7</v>
       </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B28" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>7</v>
       </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>7</v>
       </c>
-      <c r="B21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B34" t="s">
         <v>22</v>
       </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B35" t="s">
         <v>23</v>
       </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B36" t="s">
         <v>24</v>
       </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B37" t="s">
         <v>14</v>
       </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>9</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B38" t="s">
         <v>15</v>
       </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" t="s">
-        <v>35</v>
-      </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
         <v>39</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>7</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
         <v>40</v>
       </c>
-      <c r="C40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="4" t="s">
+      <c r="C54" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
         <v>41</v>
       </c>
-      <c r="C41" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="C55" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>7</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
